--- a/templates/data/disparo_atacado.xlsx
+++ b/templates/data/disparo_atacado.xlsx
@@ -569,7 +569,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13/05/2026 08:34</t>
+          <t>13/05/2026 13:18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -580,19 +580,19 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>13/05/2026 08:34</t>
+          <t>13/05/2026 13:18</t>
         </is>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr"/>
@@ -604,7 +604,7 @@
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr">
         <is>
-          <t>3EB0646D51117108018BE3</t>
+          <t>3EB0ABFDCC292B4C556FD5</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13/05/2026 08:36</t>
+          <t>13/05/2026 13:20</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -658,19 +658,19 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>13/05/2026 08:36</t>
+          <t>13/05/2026 13:20</t>
         </is>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr"/>
@@ -682,7 +682,7 @@
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr">
         <is>
-          <t>3EB029CC686B8A1D2120A5</t>
+          <t>3EB010A3EB76FA5BB25FAE</t>
         </is>
       </c>
     </row>
@@ -725,7 +725,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13/05/2026 08:37</t>
+          <t>13/05/2026 13:21</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -736,19 +736,19 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>13/05/2026 08:37</t>
+          <t>13/05/2026 13:21</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr"/>
@@ -760,7 +760,7 @@
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr">
         <is>
-          <t>3EB0B8ECA193B576F0555E</t>
+          <t>3EB08F1348E18446725E04</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13/05/2026 08:39</t>
+          <t>13/05/2026 13:23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -814,19 +814,19 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>13/05/2026 08:39</t>
+          <t>13/05/2026 13:23</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr"/>
@@ -838,7 +838,7 @@
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr">
         <is>
-          <t>A0DC6C7A9CCADB2A3F53</t>
+          <t>0DDB44E93F982F7B61D3</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>13/05/2026 08:40</t>
+          <t>13/05/2026 13:24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -892,19 +892,19 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>13/05/2026 08:40</t>
+          <t>13/05/2026 13:24</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr"/>
@@ -916,7 +916,7 @@
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr">
         <is>
-          <t>3EB0F5A649CDE85EE69BFE</t>
+          <t>3EB06081139D6023B80787</t>
         </is>
       </c>
     </row>
@@ -959,7 +959,7 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42</t>
+          <t>13/05/2026 13:26</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -970,19 +970,19 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>13/05/2026 08:42</t>
+          <t>13/05/2026 13:26</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr"/>
@@ -994,7 +994,7 @@
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr">
         <is>
-          <t>3EB0F9DFA3F7B94E383333</t>
+          <t>3EB0BAE8F066F12824D52E</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>13/05/2026 08:44</t>
+          <t>13/05/2026 13:27</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1048,19 +1048,19 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>13/05/2026 08:44</t>
+          <t>13/05/2026 13:27</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr">
         <is>
-          <t>3EB0175A122E8FBAC703B5</t>
+          <t>3EB0D5BF409721E5E8F5D7</t>
         </is>
       </c>
     </row>
@@ -1115,7 +1115,7 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>13/05/2026 08:45</t>
+          <t>13/05/2026 13:29</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1126,19 +1126,19 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>13/05/2026 08:45</t>
+          <t>13/05/2026 13:29</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr"/>
@@ -1150,7 +1150,7 @@
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr">
         <is>
-          <t>3EB014107B97E7DA0E132F</t>
+          <t>3EB069DA7FF55002F4BBCA</t>
         </is>
       </c>
     </row>
@@ -1193,7 +1193,7 @@
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>13/05/2026 08:47</t>
+          <t>13/05/2026 13:30</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1204,19 +1204,19 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>13/05/2026 08:47</t>
+          <t>13/05/2026 13:30</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr"/>
@@ -1228,7 +1228,7 @@
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr">
         <is>
-          <t>3EB0484AA3C9CD99BE8043</t>
+          <t>3EB0C40A36AFC0F1E9C3D1</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13/05/2026 08:48</t>
+          <t>13/05/2026 13:32</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1282,19 +1282,19 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>13/05/2026 08:48</t>
+          <t>13/05/2026 13:32</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr"/>
@@ -1306,7 +1306,7 @@
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3EB0F8E495F89054C3622E</t>
+          <t>3EB05E41D6D112DCEA402C</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13/05/2026 08:50</t>
+          <t>13/05/2026 13:33</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1360,19 +1360,19 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>13/05/2026 08:50</t>
+          <t>13/05/2026 13:33</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr"/>
@@ -1384,7 +1384,7 @@
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr">
         <is>
-          <t>3EB09B8CDC6C6FC93F51AD</t>
+          <t>3EB0B194D7F399AC5D43D1</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13/05/2026 08:51</t>
+          <t>13/05/2026 13:35</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1438,19 +1438,19 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>13/05/2026 08:51</t>
+          <t>13/05/2026 13:35</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr"/>
@@ -1462,7 +1462,7 @@
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr">
         <is>
-          <t>3EB0E9223459F9D17A91BE</t>
+          <t>3EB0BB08AB9744232D63E5</t>
         </is>
       </c>
     </row>
@@ -1505,7 +1505,7 @@
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13/05/2026 08:53</t>
+          <t>13/05/2026 13:36</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1516,19 +1516,19 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>13/05/2026 08:53</t>
+          <t>13/05/2026 13:36</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr"/>
@@ -1540,7 +1540,7 @@
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr">
         <is>
-          <t>3EB0C6D8482BDD8828BC30</t>
+          <t>3EB0F0BC71995D57876A77</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1583,7 @@
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>13/05/2026 08:54</t>
+          <t>13/05/2026 13:38</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1594,19 +1594,19 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13/05/2026 08:54</t>
+          <t>13/05/2026 13:38</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr"/>
@@ -1618,7 +1618,7 @@
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr">
         <is>
-          <t>3EB0267C58F52D53C10897</t>
+          <t>3EB0FBE15CDAA2208E86CC</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>13/05/2026 08:56</t>
+          <t>13/05/2026 13:39</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1672,19 +1672,19 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13/05/2026 08:56</t>
+          <t>13/05/2026 13:39</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr"/>
@@ -1696,7 +1696,7 @@
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3EB0E02BB134F9843F355D</t>
+          <t>3EB028F510C2F2338FB01B</t>
         </is>
       </c>
     </row>
@@ -1739,7 +1739,7 @@
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>13/05/2026 08:57</t>
+          <t>13/05/2026 13:41</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1750,19 +1750,19 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>13/05/2026 08:57</t>
+          <t>13/05/2026 13:41</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr"/>
@@ -1774,7 +1774,7 @@
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr">
         <is>
-          <t>3EB03334B7B2125264C2A2</t>
+          <t>3EB06349917DFF831406BD</t>
         </is>
       </c>
     </row>
@@ -1817,7 +1817,7 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>13/05/2026 08:59</t>
+          <t>13/05/2026 13:42</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1828,19 +1828,19 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>13/05/2026 08:59</t>
+          <t>13/05/2026 13:42</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr"/>
@@ -1852,7 +1852,7 @@
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr">
         <is>
-          <t>3EB094282813BE8CB711C2</t>
+          <t>3EB010C91956221E412C9D</t>
         </is>
       </c>
     </row>
@@ -1895,7 +1895,7 @@
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>13/05/2026 09:00</t>
+          <t>13/05/2026 13:44</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1906,19 +1906,19 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>13/05/2026 09:00</t>
+          <t>13/05/2026 13:44</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Disparo atacado enviado com sucesso via Z-API botões</t>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>CAMPANHA_ATACADO_BOTOES</t>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr">
         <is>
-          <t>C64E80333BF9FD9CC827</t>
+          <t>7A99AA949C7DBA9744CA</t>
         </is>
       </c>
     </row>
@@ -1967,22 +1967,50 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:45</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:45</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>3EB0301128FC08B2F33F45</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2017,22 +2045,50 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:47</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:47</t>
+        </is>
+      </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>3EB0E8B5BF9CB555F9A8F3</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2067,22 +2123,50 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:48</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:48</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>3EB02CC7F7EEA17DCB6706</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2117,7 +2201,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>DUPLICADO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -2127,7 +2211,11 @@
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Telefone duplicado na planilha ou execução</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr"/>
@@ -2167,22 +2255,50 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:50</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:50</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>3EB036346C39FF539F7B27</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2217,22 +2333,50 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:51</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:51</t>
+        </is>
+      </c>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>3EB0D14A27F0F1E57DA63E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2267,22 +2411,50 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:53</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:53</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>3EB046A3585F2BC6D6FCC5</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2317,22 +2489,50 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:54</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:54</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>3EB0684B3E3A6862CEEFB2</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2367,22 +2567,50 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:56</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:56</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>3EB055236174CB5C8FA791</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2417,22 +2645,50 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>PENDENTE</t>
+          <t>ENVIADO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:57</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
       <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>13/05/2026 13:57</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via Z-API texto simples</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_TEXTO</t>
+        </is>
+      </c>
       <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
       <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>3EB0FE2AFCB352A6CDE2C3</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">

--- a/templates/data/disparo_atacado.xlsx
+++ b/templates/data/disparo_atacado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T139"/>
+  <dimension ref="A1:U204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
           <t>ID_ENVIO</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>TIPO_ENVIO</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -607,6 +612,7 @@
           <t>3EB0ABFDCC292B4C556FD5</t>
         </is>
       </c>
+      <c r="U2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -685,6 +691,7 @@
           <t>3EB010A3EB76FA5BB25FAE</t>
         </is>
       </c>
+      <c r="U3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -763,6 +770,7 @@
           <t>3EB08F1348E18446725E04</t>
         </is>
       </c>
+      <c r="U4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -841,6 +849,7 @@
           <t>0DDB44E93F982F7B61D3</t>
         </is>
       </c>
+      <c r="U5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -919,6 +928,7 @@
           <t>3EB06081139D6023B80787</t>
         </is>
       </c>
+      <c r="U6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -997,6 +1007,7 @@
           <t>3EB0BAE8F066F12824D52E</t>
         </is>
       </c>
+      <c r="U7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1075,6 +1086,7 @@
           <t>3EB0D5BF409721E5E8F5D7</t>
         </is>
       </c>
+      <c r="U8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1153,6 +1165,7 @@
           <t>3EB069DA7FF55002F4BBCA</t>
         </is>
       </c>
+      <c r="U9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1231,6 +1244,7 @@
           <t>3EB0C40A36AFC0F1E9C3D1</t>
         </is>
       </c>
+      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1309,6 +1323,7 @@
           <t>3EB05E41D6D112DCEA402C</t>
         </is>
       </c>
+      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1387,6 +1402,7 @@
           <t>3EB0B194D7F399AC5D43D1</t>
         </is>
       </c>
+      <c r="U12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1465,6 +1481,7 @@
           <t>3EB0BB08AB9744232D63E5</t>
         </is>
       </c>
+      <c r="U13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1543,6 +1560,7 @@
           <t>3EB0F0BC71995D57876A77</t>
         </is>
       </c>
+      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1621,6 +1639,7 @@
           <t>3EB0FBE15CDAA2208E86CC</t>
         </is>
       </c>
+      <c r="U15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1699,6 +1718,7 @@
           <t>3EB028F510C2F2338FB01B</t>
         </is>
       </c>
+      <c r="U16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1777,6 +1797,7 @@
           <t>3EB06349917DFF831406BD</t>
         </is>
       </c>
+      <c r="U17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1855,6 +1876,7 @@
           <t>3EB010C91956221E412C9D</t>
         </is>
       </c>
+      <c r="U18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1933,6 +1955,7 @@
           <t>7A99AA949C7DBA9744CA</t>
         </is>
       </c>
+      <c r="U19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2011,6 +2034,7 @@
           <t>3EB0301128FC08B2F33F45</t>
         </is>
       </c>
+      <c r="U20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2089,6 +2113,7 @@
           <t>3EB0E8B5BF9CB555F9A8F3</t>
         </is>
       </c>
+      <c r="U21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2167,6 +2192,7 @@
           <t>3EB02CC7F7EEA17DCB6706</t>
         </is>
       </c>
+      <c r="U22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2221,6 +2247,7 @@
       <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2299,6 +2326,7 @@
           <t>3EB036346C39FF539F7B27</t>
         </is>
       </c>
+      <c r="U24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2377,6 +2405,7 @@
           <t>3EB0D14A27F0F1E57DA63E</t>
         </is>
       </c>
+      <c r="U25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2455,6 +2484,7 @@
           <t>3EB046A3585F2BC6D6FCC5</t>
         </is>
       </c>
+      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2533,6 +2563,7 @@
           <t>3EB0684B3E3A6862CEEFB2</t>
         </is>
       </c>
+      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2611,6 +2642,7 @@
           <t>3EB055236174CB5C8FA791</t>
         </is>
       </c>
+      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2689,6 +2721,7 @@
           <t>3EB0FE2AFCB352A6CDE2C3</t>
         </is>
       </c>
+      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2767,6 +2800,7 @@
           <t>3EB0F6D035DEB4C4739576</t>
         </is>
       </c>
+      <c r="U30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2845,6 +2879,7 @@
           <t>3EB0EE417E9C2170D2B627</t>
         </is>
       </c>
+      <c r="U31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2923,6 +2958,7 @@
           <t>3EB0C41EED8388306D4F20</t>
         </is>
       </c>
+      <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3001,6 +3037,7 @@
           <t>110CD93D36A7B06AED18</t>
         </is>
       </c>
+      <c r="U33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3079,6 +3116,7 @@
           <t>3EB0003D53006750A008F8</t>
         </is>
       </c>
+      <c r="U34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3157,6 +3195,7 @@
           <t>3EB0D50F3E36287B67907B</t>
         </is>
       </c>
+      <c r="U35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3235,6 +3274,7 @@
           <t>3EB0E39CC06009299EDCF6</t>
         </is>
       </c>
+      <c r="U36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3313,6 +3353,7 @@
           <t>3EB0D5D14D9E145D03511F</t>
         </is>
       </c>
+      <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3391,6 +3432,7 @@
           <t>3EB0BA53922EAC3D47B425</t>
         </is>
       </c>
+      <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3469,6 +3511,7 @@
           <t>3EB06755768EE0E86C641F</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3547,6 +3590,7 @@
           <t>3EB0C73F82560D1B670F72</t>
         </is>
       </c>
+      <c r="U40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3625,6 +3669,7 @@
           <t>3EB0597147242DD30D4A9C</t>
         </is>
       </c>
+      <c r="U41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3703,6 +3748,7 @@
           <t>3EB0AC24D32E2F4F0A63D1</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3781,6 +3827,7 @@
           <t>3EB0E22626BE0275685336</t>
         </is>
       </c>
+      <c r="U43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3859,6 +3906,7 @@
           <t>3EB0162B289147DB663682</t>
         </is>
       </c>
+      <c r="U44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3937,6 +3985,7 @@
           <t>3EB082B7D32D1BF0E92E91</t>
         </is>
       </c>
+      <c r="U45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4015,6 +4064,7 @@
           <t>3EB026F9BE9AD5B1377A3D</t>
         </is>
       </c>
+      <c r="U46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4093,6 +4143,7 @@
           <t>3EB0FCD2C1B9BEB402068D</t>
         </is>
       </c>
+      <c r="U47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4171,6 +4222,7 @@
           <t>3EB0141E08347D5B9FE7E2</t>
         </is>
       </c>
+      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4249,6 +4301,7 @@
           <t>3EB0D11F6EBDCA1C94BF1C</t>
         </is>
       </c>
+      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4327,6 +4380,7 @@
           <t>3EB08CCA4C27A4C9EA9CA2</t>
         </is>
       </c>
+      <c r="U50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4405,6 +4459,7 @@
           <t>3EB0941DD17965CCD436DC</t>
         </is>
       </c>
+      <c r="U51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4483,6 +4538,7 @@
           <t>3EB0C073F1892DC567764F</t>
         </is>
       </c>
+      <c r="U52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4561,6 +4617,7 @@
           <t>16B4665EFB8F3FCB9D99</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4639,6 +4696,7 @@
           <t>3EB01C91265BD0F09BCF58</t>
         </is>
       </c>
+      <c r="U54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4717,6 +4775,7 @@
           <t>3EB0BC5FF5C6DC4E6EF5F3</t>
         </is>
       </c>
+      <c r="U55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4795,6 +4854,7 @@
           <t>3EB0020B6847723BDD0B74</t>
         </is>
       </c>
+      <c r="U56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4873,6 +4933,7 @@
           <t>3EB0035E1CE2ACEECC50A0</t>
         </is>
       </c>
+      <c r="U57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4951,6 +5012,7 @@
           <t>3EB010856A505A512CEE1E</t>
         </is>
       </c>
+      <c r="U58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5029,6 +5091,7 @@
           <t>3EB052764C9078DFC13AD3</t>
         </is>
       </c>
+      <c r="U59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -5107,6 +5170,7 @@
           <t>3EB0182D99AFB58292ABB6</t>
         </is>
       </c>
+      <c r="U60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5185,6 +5249,7 @@
           <t>3EB066F8751F34AF8913BF</t>
         </is>
       </c>
+      <c r="U61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5263,6 +5328,7 @@
           <t>3EB0FAE7A785CF2C5581CD</t>
         </is>
       </c>
+      <c r="U62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5341,6 +5407,7 @@
           <t>3EB01ADA06FC07524D4847</t>
         </is>
       </c>
+      <c r="U63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5419,6 +5486,7 @@
           <t>3EB00B7B1DD7269C1F5E5E</t>
         </is>
       </c>
+      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5473,6 +5541,7 @@
       <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5551,6 +5620,7 @@
           <t>3EB00D58E0AF2CF28DAF6C</t>
         </is>
       </c>
+      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5629,6 +5699,7 @@
           <t>3EB00DBEF47975136D7BC7</t>
         </is>
       </c>
+      <c r="U67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5707,6 +5778,7 @@
           <t>3EB0AA397F2C217D21946B</t>
         </is>
       </c>
+      <c r="U68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5785,6 +5857,7 @@
           <t>3EB011D6306D070AFAA2B6</t>
         </is>
       </c>
+      <c r="U69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5863,6 +5936,7 @@
           <t>3EB0C6F897802D9C435C8C</t>
         </is>
       </c>
+      <c r="U70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5941,6 +6015,7 @@
           <t>3EB0D8570E3E1E4F9F6132</t>
         </is>
       </c>
+      <c r="U71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -6019,6 +6094,7 @@
           <t>3EB07143AFA17305DC1111</t>
         </is>
       </c>
+      <c r="U72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -6097,6 +6173,7 @@
           <t>3EB00A7E072AC673B3858A</t>
         </is>
       </c>
+      <c r="U73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -6175,6 +6252,7 @@
           <t>3EB089CBD4505411A02FC3</t>
         </is>
       </c>
+      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -6253,6 +6331,7 @@
           <t>3EB06AED0EE90CD907E53E</t>
         </is>
       </c>
+      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -6331,6 +6410,7 @@
           <t>3EB0FBDF8C9957A890B9C3</t>
         </is>
       </c>
+      <c r="U76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6409,6 +6489,7 @@
           <t>3EB0E7DE7A106B584F2E2E</t>
         </is>
       </c>
+      <c r="U77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6487,6 +6568,7 @@
           <t>3EB06FF614B3841E7BCA8F</t>
         </is>
       </c>
+      <c r="U78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6565,6 +6647,7 @@
           <t>3EB03F28FB04D28A1B2D34</t>
         </is>
       </c>
+      <c r="U79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6643,6 +6726,7 @@
           <t>3EB0E77AD8E744403C43B3</t>
         </is>
       </c>
+      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6721,6 +6805,7 @@
           <t>3EB04839CE41B1524DA80B</t>
         </is>
       </c>
+      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6799,6 +6884,7 @@
           <t>3EB07B90F146EE8F749603</t>
         </is>
       </c>
+      <c r="U82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6877,6 +6963,7 @@
           <t>3EB0331FAFE20CCE8A8EC2</t>
         </is>
       </c>
+      <c r="U83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6955,6 +7042,7 @@
           <t>3EB0A337FEAFF5EF4B575A</t>
         </is>
       </c>
+      <c r="U84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -7033,6 +7121,7 @@
           <t>3EB0C6128D6024BD182AF1</t>
         </is>
       </c>
+      <c r="U85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -7111,6 +7200,7 @@
           <t>3EB02A61E0CA5A4E76BD82</t>
         </is>
       </c>
+      <c r="U86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -7189,6 +7279,7 @@
           <t>3EB008306B8B433A2767BA</t>
         </is>
       </c>
+      <c r="U87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -7267,6 +7358,7 @@
           <t>3EB0BF4848DAD0B0C67C06</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -7345,6 +7437,7 @@
           <t>3EB0891559C7215F42743A</t>
         </is>
       </c>
+      <c r="U89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7423,6 +7516,7 @@
           <t>3EB0D868E406368DDE6D65</t>
         </is>
       </c>
+      <c r="U90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -7501,6 +7595,7 @@
           <t>3EB0734F6ACA76257F126E</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7579,6 +7674,7 @@
           <t>9B3CFD725B4C671321E2</t>
         </is>
       </c>
+      <c r="U92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7657,6 +7753,7 @@
           <t>3EB04CC4F6B3C4F3094F5F</t>
         </is>
       </c>
+      <c r="U93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7735,6 +7832,7 @@
           <t>3EB0C977C158786945D6D1</t>
         </is>
       </c>
+      <c r="U94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7813,6 +7911,7 @@
           <t>3EB02EA02FD1440D0B5DF6</t>
         </is>
       </c>
+      <c r="U95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7891,6 +7990,7 @@
           <t>3EB0CD258E6BD152BDF14C</t>
         </is>
       </c>
+      <c r="U96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7969,6 +8069,7 @@
           <t>3EB03929D7FCCB24C11564</t>
         </is>
       </c>
+      <c r="U97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -8047,6 +8148,7 @@
           <t>3EB056A8842E7200E441C6</t>
         </is>
       </c>
+      <c r="U98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -8125,6 +8227,7 @@
           <t>3EB0EE4B155CD52B38F668</t>
         </is>
       </c>
+      <c r="U99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -8203,6 +8306,7 @@
           <t>7414081B1D1279F027B1</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -8281,6 +8385,7 @@
           <t>6E728898B5801A14C448</t>
         </is>
       </c>
+      <c r="U101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -8359,6 +8464,7 @@
           <t>A7CD408DBF5592129537</t>
         </is>
       </c>
+      <c r="U102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -8437,6 +8543,7 @@
           <t>757CA595FF657F57FF4C</t>
         </is>
       </c>
+      <c r="U103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -8515,6 +8622,7 @@
           <t>7BA1B7D375BA05A86D93</t>
         </is>
       </c>
+      <c r="U104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8593,6 +8701,7 @@
           <t>A8426226F2B13870359F</t>
         </is>
       </c>
+      <c r="U105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8671,6 +8780,7 @@
           <t>15E3AE87D58394D96772</t>
         </is>
       </c>
+      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8749,6 +8859,7 @@
           <t>965020FD41FA32DBC5E3</t>
         </is>
       </c>
+      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8827,6 +8938,7 @@
           <t>474729C3F7C6A1D3D8A8</t>
         </is>
       </c>
+      <c r="U108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8905,6 +9017,7 @@
           <t>04CEF99105BDB34A727D</t>
         </is>
       </c>
+      <c r="U109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8983,6 +9096,7 @@
           <t>931037AC1517E8915D8C</t>
         </is>
       </c>
+      <c r="U110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -9061,6 +9175,7 @@
           <t>A47C8D3A0F47423E6BA7</t>
         </is>
       </c>
+      <c r="U111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -9139,6 +9254,7 @@
           <t>5F2B3A9CCA7DCD24614B</t>
         </is>
       </c>
+      <c r="U112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -9217,6 +9333,7 @@
           <t>69760D7AF4408186756B</t>
         </is>
       </c>
+      <c r="U113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -9295,6 +9412,7 @@
           <t>455FF48A245E036501E7</t>
         </is>
       </c>
+      <c r="U114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -9373,6 +9491,7 @@
           <t>37EA3C9B2E380DF5FABD</t>
         </is>
       </c>
+      <c r="U115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -9451,6 +9570,7 @@
           <t>352F2C3E6B7D7AD79A12</t>
         </is>
       </c>
+      <c r="U116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -9529,6 +9649,7 @@
           <t>E2F409FF3FF321707DE4</t>
         </is>
       </c>
+      <c r="U117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9607,6 +9728,7 @@
           <t>DA35D1E31C998A14654F</t>
         </is>
       </c>
+      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9685,6 +9807,7 @@
           <t>F81C1660B76BCBE720E2</t>
         </is>
       </c>
+      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9763,6 +9886,7 @@
           <t>F9BF02E57934B4C7CBED</t>
         </is>
       </c>
+      <c r="U120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9841,6 +9965,7 @@
           <t>530CB3CBEBAB4B474737</t>
         </is>
       </c>
+      <c r="U121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -9919,6 +10044,7 @@
           <t>E5B7D556BE647F5A1A15</t>
         </is>
       </c>
+      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -9997,6 +10123,7 @@
           <t>DE4B1CA5F04471EDCD3B</t>
         </is>
       </c>
+      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -10075,6 +10202,7 @@
           <t>3C4978ADCFDAEFAE6602</t>
         </is>
       </c>
+      <c r="U124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -10153,6 +10281,7 @@
           <t>3EB0BB1FD192255CCB8D67</t>
         </is>
       </c>
+      <c r="U125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -10231,6 +10360,7 @@
           <t>3EB0C7E8DF95C56F3753C1</t>
         </is>
       </c>
+      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -10309,6 +10439,7 @@
           <t>3EB0BD8841B0BF99D62BED</t>
         </is>
       </c>
+      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -10387,6 +10518,7 @@
           <t>3EB0042FA9753576A76428</t>
         </is>
       </c>
+      <c r="U128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -10465,6 +10597,7 @@
           <t>3EB07CF619429EE60B592F</t>
         </is>
       </c>
+      <c r="U129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -10543,6 +10676,7 @@
           <t>59B99D09899E3EC93F2A</t>
         </is>
       </c>
+      <c r="U130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -10621,6 +10755,7 @@
           <t>3EB06EFB00819DA60D6FF0</t>
         </is>
       </c>
+      <c r="U131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -10699,6 +10834,7 @@
           <t>3EB0E20CE6E8EF8743563F</t>
         </is>
       </c>
+      <c r="U132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -10777,6 +10913,7 @@
           <t>3EB0789CCE719DED9B6CA6</t>
         </is>
       </c>
+      <c r="U133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -10855,6 +10992,7 @@
           <t>3EB090DB1F2612D71B3FCE</t>
         </is>
       </c>
+      <c r="U134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -10933,6 +11071,7 @@
           <t>3EB021B73AE3912F0AE749</t>
         </is>
       </c>
+      <c r="U135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -11011,6 +11150,7 @@
           <t>3EB0B56174138329E22AB9</t>
         </is>
       </c>
+      <c r="U136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -11089,6 +11229,7 @@
           <t>3EB0A63C49739351B7D5FC</t>
         </is>
       </c>
+      <c r="U137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -11143,6 +11284,7 @@
       <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -11219,6 +11361,5850 @@
       <c r="T139" t="inlineStr">
         <is>
           <t>3EB0C73363ED2E6C9B8525</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Ts Motos peças e serviços</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>(94) 99269-7251</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>5594992697251</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:18</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:18</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>568B716A11D56256002D</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Maranata moto peças e serviços</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>(94) 98406-3289</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>5594984063289</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:20</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:20</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>3EB089BE2DBBB78E057F3D</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Pop Motos Peças E Serviços</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>(94) 99158-6592</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>5594991586592</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:21</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:21</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>3EB02919DAA509269B1354</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>R Moto Peças</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>(94) 99111-4976</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>5594991114976</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:23</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:23</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>3EB05D150C296308F51895</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>JF MOTO PEÇAS</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>(94) 99280-4097</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>5594992804097</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:24</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:24</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>3EB01CE28DFEE51295DE99</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Júnior Motos</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>(94) 99213-4807</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>5594992134807</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:26</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:26</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>3EB0E076965754114E0BB9</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Maranata moto peças e serviços</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>(94) 98406-3289</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>5594984063289</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>Telefone duplicado na planilha ou execução</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr"/>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr"/>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CM MOTOS Nova Marabá</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>(94) 98101-4808</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>5594981014808</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:27</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:27</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>3EB08DD863411F49739948</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Irmãos Carvalho Atacado</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>(94) 98416-3458</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>5594984163458</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:29</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:29</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>3EB0EFA9A11499A85DADD8</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Pedalmotos</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>(94) 99176-5776</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>5594991765776</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>3EB0AFE4F1530E08DB586A</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Norte Sul Peças</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>(94) 99132-6918</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>5594991326918</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:32</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:32</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>3EB0BA55A88933276D1162</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>D.J MOTOPEÇAS</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>(94) 99260-3103</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>5594992603103</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:33</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:33</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>3EB0484BEEF7F3BBF3F72C</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>JD moto peças</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>(94) 99108-1354</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>5594991081354</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:35</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:35</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>3EB01D24A4E4548D0809A2</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Bicicletão Bike Shop e Moto Peças - Marabá</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Serviço de distribuição</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>(94) 98430-0312</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>5594984300312</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:36</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:36</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>3EB0A900269C8537B610AA</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>FRANCIS MOTOS</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>(94) 99144-2956</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>5594991442956</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:38</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:38</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>3EB01D89A44018A24BF8D9</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>RT moto peças</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>(94) 99285-9566</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>5594992859566</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:39</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:39</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>2913FF1F13AD1E750F67</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>CM MOTOS Cidade Nova</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>(94) 99265-8119</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>5594992658119</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:41</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:41</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>3EB071B5944AB2CC138AB9</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>CM MOTOS Cidade Nova</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>(94) 99265-8119</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>5594992658119</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>Telefone duplicado na planilha ou execução</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr"/>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr"/>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>3D Moto Peças E Oficina</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>(94) 99107-7144</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>5594991077144</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:42</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:42</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr">
+        <is>
+          <t>3EB0309CE9E31788C3DDA6</t>
+        </is>
+      </c>
+      <c r="U158" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>NEGÃO MOTO PECAS peças e assessórios</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>(94) 99166-8721</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>5594991668721</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:44</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:44</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr">
+        <is>
+          <t>3EB0E9DB50046C7BD3AABE</t>
+        </is>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Marquinho Motos</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>(94) 99191-3285</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>5594991913285</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:45</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:45</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>3EB01A8A8EC03A0C9053C7</t>
+        </is>
+      </c>
+      <c r="U160" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>JJ Moto Peças Parauapebas - Rio Verde</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>(94) 99285-6543</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>5594992856543</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:47</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:47</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
+        <is>
+          <t>3EB0AFE1E300F8972F7E93</t>
+        </is>
+      </c>
+      <c r="U161" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>SPORT MOTO</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>(94) 98807-2138</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>5594988072138</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:48</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:48</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr">
+        <is>
+          <t>3EB07ED7D89867F238B117</t>
+        </is>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>M3 Motopeças Bairro Araguaia</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>(94) 99121-2008</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>5594991212008</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:50</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:50</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr">
+        <is>
+          <t>3EB0C263565CA7931079E5</t>
+        </is>
+      </c>
+      <c r="U163" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Fox Motos</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>(94) 99179-6829</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>5594991796829</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:51</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:51</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr">
+        <is>
+          <t>3EB09AA9C0F3FEB6D2F6A6</t>
+        </is>
+      </c>
+      <c r="U164" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Centro motos Motos</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>(94) 99135-8667</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>5594991358667</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:53</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:53</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>3EB01465AEFD3C10283472</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>M-Tech Motopeças</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>(94) 99185-3161</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>5594991853161</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:54</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:54</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr"/>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr">
+        <is>
+          <t>3EB0DD662E412CE5891A0C</t>
+        </is>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Raposão moto peças</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>(94) 98406-8238</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>5594984068238</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:56</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:56</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>3EB04EF44AAA5E5A157CF1</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>BB Moto Peças São Félix</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>(94) 99125-0689</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>5594991250689</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:57</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:57</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>3EB0031603A4D49C610E42</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Papa-Léguas Motos</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>(94) 98807-4514</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>5594988074514</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:59</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>15/05/2026 08:59</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>3EB09052A70AB1E386CF39</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Jacaré moto peça</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>(94) 99254-7660</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>5594992547660</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:00</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:00</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr"/>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>974616B1F8234B4C50E4</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Carlito Moto Peças e Acessorios</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>(94) 99219-6839</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>5594992196839</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:50</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:50</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>453CB555758FDB52F38C</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>LS Motos Peças e Serviços Em Geral</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Mecânica para carros</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>(94) 99146-2295</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>5594991462295</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:51</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:51</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr"/>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>2490E97E26B49202CC14</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>WD MOTOS</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>(94) 99178-4070</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>5594991784070</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:53</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:53</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>BE69FA13BCBE323E89B8</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Lider Distribuidora de Moto Peças</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Serviço de distribuição</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>(94) 99148-3644</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>5594991483644</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:54</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:54</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>6549BC00DFD4D43A9858</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Ts motos Ltda</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Concessionária de motocicletas</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>(94) 3426-1312</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>559434261312</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:56</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:56</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>317AC42AE75CC2DD313A</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Hugo Motos | Xinguara</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>(94) 99176-6768</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>5594991766768</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:57</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:57</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr">
+        <is>
+          <t>EA37E9AFF3CC33F07729</t>
+        </is>
+      </c>
+      <c r="U176" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Destak motos Peças e Acessórios</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>(94) 99199-6164</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>5594991996164</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:59</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>15/05/2026 09:59</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr">
+        <is>
+          <t>9BF41A5BD34C2A2C6635</t>
+        </is>
+      </c>
+      <c r="U177" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>DAKAR MOTO PEÇAS</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>(94) 99116-4694</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>5594991164694</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:00</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:00</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr">
+        <is>
+          <t>304517AC200BBE904BFD</t>
+        </is>
+      </c>
+      <c r="U178" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Líder Motos</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>(94) 99165-8388</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>5594991658388</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:02</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:02</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>564F7A6163A25ABAD34A</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Planeta Motos</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>(94) 3426-2496</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>559434262496</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:03</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:03</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr">
+        <is>
+          <t>052CBDE17B6D2130E640</t>
+        </is>
+      </c>
+      <c r="U180" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>RodaLivre Moto Peças</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>(94) 99253-8581</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>5594992538581</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:05</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:05</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr">
+        <is>
+          <t>4147012FAD28B3B7400D</t>
+        </is>
+      </c>
+      <c r="U181" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Rocha Motos Xinguara - Peças Novas e Usadas - Oficina de Motos</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>(94) 99105-1110</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>5594991051110</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:06</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:06</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr">
+        <is>
+          <t>59E6BC45932A268D1C14</t>
+        </is>
+      </c>
+      <c r="U182" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Loja bahia motos</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>(94) 99142-8335</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>5594991428335</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:08</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:08</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr">
+        <is>
+          <t>D420345E1AB3CA0D03C2</t>
+        </is>
+      </c>
+      <c r="U183" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Imperial Moto Peças</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Mecânico</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>(94) 99234-4710</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>5594992344710</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:09</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:09</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr">
+        <is>
+          <t>20D44309895BF09520DD</t>
+        </is>
+      </c>
+      <c r="U184" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Moto center</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>(94) 99287-6228</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>5594992876228</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:11</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:11</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>F741ADDA546FE2F5684B</t>
+        </is>
+      </c>
+      <c r="U185" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Box 22 Moto Peças</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>(94) 99267-5498</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>5594992675498</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:12</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:12</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr">
+        <is>
+          <t>0911258B12BABD54C1F1</t>
+        </is>
+      </c>
+      <c r="U186" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Baguá Bicicletas e Motos</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Loja de bicicleta</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>(94) 99154-9149</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>5594991549149</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:14</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:14</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr">
+        <is>
+          <t>97D86694189DF144E75F</t>
+        </is>
+      </c>
+      <c r="U187" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Ph moto show</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>(94) 99136-3761</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>5594991363761</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>XINGUARA</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:15</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:15</t>
+        </is>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr">
+        <is>
+          <t>3BCD71F04AAE38460B6A</t>
+        </is>
+      </c>
+      <c r="U188" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Líder Motopeças</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>(94) 98125-2504</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>5594981252504</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:17</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:17</t>
+        </is>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P189" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>B022452A52A00B4E95BB</t>
+        </is>
+      </c>
+      <c r="U189" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>MOTO PAI PEÇAS E ACESSÓRIOS</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>(94) 98141-7159</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>5594981417159</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:18</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:18</t>
+        </is>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr">
+        <is>
+          <t>3A6C3347040174349746</t>
+        </is>
+      </c>
+      <c r="U190" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Trilha Motos</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>(94) 98409-2776</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>5594984092776</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:20</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:20</t>
+        </is>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P191" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr">
+        <is>
+          <t>079662DFD7892C2298C4</t>
+        </is>
+      </c>
+      <c r="U191" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Izack Moto Peças PA 279 Vila Carapanã</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>(94) 99292-6606</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>5594992926606</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:21</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:21</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P192" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr">
+        <is>
+          <t>BF58A2DA70567AD9DFDA</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>Eskilo moto peças</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>(94) 98134-1717</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>5594981341717</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:23</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:23</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+      <c r="N193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P193" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q193" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R193" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>AA9F320FC4B2FE9034D9</t>
+        </is>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Promotos</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>(94) 98410-3888</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>5594984103888</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:24</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:24</t>
+        </is>
+      </c>
+      <c r="M194" t="inlineStr"/>
+      <c r="N194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P194" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R194" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T194" t="inlineStr">
+        <is>
+          <t>276577003EB31520D7FF</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Xingu borracharia e moto peças</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>(94) 98122-3133</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>5594981223133</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:26</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:26</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr"/>
+      <c r="N195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P195" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q195" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S195" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T195" t="inlineStr">
+        <is>
+          <t>3221BAD19796E866D055</t>
+        </is>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Az Motos</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>(94) 98403-2319</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>5594984032319</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:27</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:27</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr"/>
+      <c r="N196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P196" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R196" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T196" t="inlineStr">
+        <is>
+          <t>D03D13AAB099CA7E4FD3</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Saara Motos</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>(94) 98107-1328</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>5594981071328</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:29</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:29</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr"/>
+      <c r="N197" t="inlineStr"/>
+      <c r="O197" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P197" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R197" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S197" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T197" t="inlineStr">
+        <is>
+          <t>1F3713C4CF8B11BB57CC</t>
+        </is>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Vanin Moto Pecas</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>(94) 98114-7055</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>5594981147055</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:30</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:30</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr"/>
+      <c r="N198" t="inlineStr"/>
+      <c r="O198" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R198" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T198" t="inlineStr">
+        <is>
+          <t>96C1840DAAC1F25B58A2</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>piloto moto peçcas</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>(62) 98507-5628</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>5562985075628</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:32</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:32</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr"/>
+      <c r="N199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P199" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R199" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T199" t="inlineStr">
+        <is>
+          <t>7342B97B62743196BEC0</t>
+        </is>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Aurélio Miguel Moto Peças e Borracharia</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>(94) 98418-2908</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>5594984182908</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:33</t>
+        </is>
+      </c>
+      <c r="M200" t="inlineStr"/>
+      <c r="N200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R200" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T200" t="inlineStr">
+        <is>
+          <t>0345AEC315C26BDF61F1</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Wr moto peças</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>(94) 98111-4761</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>5594981114761</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:35</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:35</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+      <c r="N201" t="inlineStr"/>
+      <c r="O201" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R201" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S201" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T201" t="inlineStr">
+        <is>
+          <t>7E4023BBC073076FB2FB</t>
+        </is>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Cia Motos</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>(94) 3365-4014</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>559433654014</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:36</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:36</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr"/>
+      <c r="N202" t="inlineStr"/>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T202" t="inlineStr">
+        <is>
+          <t>C865C10849323BB193D2</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Infinity Motos</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>(94) 98123-6276</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>5594981236276</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:38</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:38</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
+      <c r="O203" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R203" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S203" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T203" t="inlineStr">
+        <is>
+          <t>8D99F2E9DF13A7E8706A</t>
+        </is>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Moto Forte</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>(94) 98146-5935</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>5594981465935</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>SAO FELIX</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:39</t>
+        </is>
+      </c>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr">
+        <is>
+          <t>15/05/2026 10:39</t>
+        </is>
+      </c>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R204" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S204" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T204" t="inlineStr">
+        <is>
+          <t>42209504BCCD13670E59</t>
+        </is>
+      </c>
+      <c r="U204" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
         </is>
       </c>
     </row>

--- a/templates/data/disparo_atacado.xlsx
+++ b/templates/data/disparo_atacado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U204"/>
+  <dimension ref="A1:U243"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17208,6 +17208,3555 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Atacadão Moto Peças</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>(99) 98526-2063</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>5599985262063</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:17</t>
+        </is>
+      </c>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:17</t>
+        </is>
+      </c>
+      <c r="M205" t="inlineStr"/>
+      <c r="N205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R205" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S205" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T205" t="inlineStr">
+        <is>
+          <t>8A9BB54EB1B3F52A4C1E</t>
+        </is>
+      </c>
+      <c r="U205" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Cortez Motos - Rua Ceará</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>(99) 3524-5888</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>559935245888</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:18</t>
+        </is>
+      </c>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:18</t>
+        </is>
+      </c>
+      <c r="M206" t="inlineStr"/>
+      <c r="N206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R206" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S206" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T206" t="inlineStr">
+        <is>
+          <t>3EB0F9E0423C6604D8D887</t>
+        </is>
+      </c>
+      <c r="U206" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Atacadão Moto Peças 2</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>(99) 98528-1303</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>5599985281303</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:20</t>
+        </is>
+      </c>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:20</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+      <c r="N207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R207" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S207" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T207" t="inlineStr">
+        <is>
+          <t>3EB0FABE74F8CA6CEF2F1F</t>
+        </is>
+      </c>
+      <c r="U207" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Motor peças motosserras em Imperatriz - roçadeiras em Imperatriz -motores estacionário em Imperatriz</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Fornecedor de equipamentos agrícolas</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>(99) 3525-7772</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>559935257772</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:21</t>
+        </is>
+      </c>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:21</t>
+        </is>
+      </c>
+      <c r="M208" t="inlineStr"/>
+      <c r="N208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q208" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R208" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T208" t="inlineStr">
+        <is>
+          <t>3EB0CCF932094BE85DAC44</t>
+        </is>
+      </c>
+      <c r="U208" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Tony Moto Peças</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Loja de autopeças</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>(99) 98242-9668</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>5599982429668</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:23</t>
+        </is>
+      </c>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:23</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+      <c r="N209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R209" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S209" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T209" t="inlineStr">
+        <is>
+          <t>3EB0C9788463329C7C080C</t>
+        </is>
+      </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Luso Motos Comércio e Distribuição Ltda</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>(99) 3524-4505</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>559935244505</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:24</t>
+        </is>
+      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:24</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+      <c r="N210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R210" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S210" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T210" t="inlineStr">
+        <is>
+          <t>3EB00B1E417FBE8E33D212</t>
+        </is>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>STRELA MOTO PEÇAS - Atacado e Varejo</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>(99) 98433-1186</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>5599984331186</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:26</t>
+        </is>
+      </c>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:26</t>
+        </is>
+      </c>
+      <c r="M211" t="inlineStr"/>
+      <c r="N211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R211" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S211" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T211" t="inlineStr">
+        <is>
+          <t>3EB06F060AD7776C02388F</t>
+        </is>
+      </c>
+      <c r="U211" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>KSS MOTOS CEARÁ ITZ</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>(99) 98476-2923</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>5599984762923</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:27</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:27</t>
+        </is>
+      </c>
+      <c r="M212" t="inlineStr"/>
+      <c r="N212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R212" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S212" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T212" t="inlineStr">
+        <is>
+          <t>3EB0B2C3BB40400D02488C</t>
+        </is>
+      </c>
+      <c r="U212" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Damásio Motopeças Imperatriz</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>(86) 3131-8320</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>558631318320</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:29</t>
+        </is>
+      </c>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:29</t>
+        </is>
+      </c>
+      <c r="M213" t="inlineStr"/>
+      <c r="N213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R213" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S213" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T213" t="inlineStr">
+        <is>
+          <t>3EB0AC7E44C4339432D0DB</t>
+        </is>
+      </c>
+      <c r="U213" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>s.a moto pecas</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>(99) 98543-3274</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>5599985433274</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+      <c r="N214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q214" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R214" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T214" t="inlineStr">
+        <is>
+          <t>3EB0EDF7499D737A99C175</t>
+        </is>
+      </c>
+      <c r="U214" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Moto Center</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>(99) 98218-9990</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>5599982189990</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:32</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:32</t>
+        </is>
+      </c>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q215" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R215" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T215" t="inlineStr">
+        <is>
+          <t>3EB09391E2472F76075D73</t>
+        </is>
+      </c>
+      <c r="U215" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>MOTO PEÇAS REVISÃO</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>(99) 99106-1317</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>5599991061317</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:33</t>
+        </is>
+      </c>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:33</t>
+        </is>
+      </c>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R216" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S216" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T216" t="inlineStr">
+        <is>
+          <t>3EB0F11BD5A5139EA0419C</t>
+        </is>
+      </c>
+      <c r="U216" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Piu Motos Peças e Preparações</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>(99) 98480-7257</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>5599984807257</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:35</t>
+        </is>
+      </c>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr">
+        <is>
+          <t>18/05/2026 08:35</t>
+        </is>
+      </c>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S217" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T217" t="inlineStr">
+        <is>
+          <t>3EB0D9E6BEF56E48AD81C8</t>
+        </is>
+      </c>
+      <c r="U217" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Ferrari Moto Peças</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>(99) 3541-5641</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>559935415641</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:46</t>
+        </is>
+      </c>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:46</t>
+        </is>
+      </c>
+      <c r="M218" t="inlineStr"/>
+      <c r="N218" t="inlineStr"/>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R218" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S218" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T218" t="inlineStr">
+        <is>
+          <t>3EB0A20509F12D4134A96D</t>
+        </is>
+      </c>
+      <c r="U218" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>KSS MOTOS BALSAS</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>(99) 98480-8984</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>5599984808984</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:47</t>
+        </is>
+      </c>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:47</t>
+        </is>
+      </c>
+      <c r="M219" t="inlineStr"/>
+      <c r="N219" t="inlineStr"/>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q219" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R219" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S219" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T219" t="inlineStr">
+        <is>
+          <t>3EB0DE09035B7F8BC05AB8</t>
+        </is>
+      </c>
+      <c r="U219" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>MF Motos</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Loja</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>(99) 3541-1446</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>559935411446</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:49</t>
+        </is>
+      </c>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:49</t>
+        </is>
+      </c>
+      <c r="M220" t="inlineStr"/>
+      <c r="N220" t="inlineStr"/>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q220" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R220" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T220" t="inlineStr">
+        <is>
+          <t>D463C672ECE06BA66254</t>
+        </is>
+      </c>
+      <c r="U220" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Motoka Peças</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>(99) 98818-5632</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>5599988185632</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:50</t>
+        </is>
+      </c>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:50</t>
+        </is>
+      </c>
+      <c r="M221" t="inlineStr"/>
+      <c r="N221" t="inlineStr"/>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q221" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R221" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T221" t="inlineStr">
+        <is>
+          <t>3EB0479AFC8BB7D2BF3B6A</t>
+        </is>
+      </c>
+      <c r="U221" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Mix Moto Peças</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>(99) 3541-9721</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>559935419721</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:52</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:52</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr"/>
+      <c r="N222" t="inlineStr"/>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q222" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R222" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T222" t="inlineStr">
+        <is>
+          <t>3EB0186F9620BDC4EE36C3</t>
+        </is>
+      </c>
+      <c r="U222" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Mc Motopeças</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>(99) 3541-9246</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>559935419246</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:53</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:53</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr"/>
+      <c r="N223" t="inlineStr"/>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q223" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R223" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T223" t="inlineStr">
+        <is>
+          <t>3EB0DEBBA2848D17704804</t>
+        </is>
+      </c>
+      <c r="U223" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Universal Motos</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>(99) 3541-6722</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>559935416722</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:55</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:55</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr"/>
+      <c r="N224" t="inlineStr"/>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q224" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R224" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T224" t="inlineStr">
+        <is>
+          <t>3EB0999496E4D8A013B1CC</t>
+        </is>
+      </c>
+      <c r="U224" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>SANTOS MOTO PEÇAS</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Loja</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>(99) 99902-0544</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>5599999020544</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:56</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:56</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+      <c r="N225" t="inlineStr"/>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q225" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R225" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T225" t="inlineStr">
+        <is>
+          <t>3EB07193158BF45DC7DE3A</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>HF Moto Peças</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>(99) 98826-4757</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>5599988264757</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:58</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:58</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr"/>
+      <c r="N226" t="inlineStr"/>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q226" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R226" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T226" t="inlineStr">
+        <is>
+          <t>3EB078375EDF0706EF84A1</t>
+        </is>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>R-A MOTO PEÇAS</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>(99) 98180-8079</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>5599981808079</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:59</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>18/05/2026 10:59</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+      <c r="N227" t="inlineStr"/>
+      <c r="O227" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q227" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R227" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T227" t="inlineStr">
+        <is>
+          <t>3EB07668416F078DCBAF3B</t>
+        </is>
+      </c>
+      <c r="U227" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>Rafael Moto Peças</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>(99) 99651-3788</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>5599996513788</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>18/05/2026 11:01</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>18/05/2026 11:01</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr"/>
+      <c r="N228" t="inlineStr"/>
+      <c r="O228" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q228" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R228" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T228" t="inlineStr">
+        <is>
+          <t>3EB07287A8B18214059FB4</t>
+        </is>
+      </c>
+      <c r="U228" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Graúna Motos</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Concessionária Honda</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>(99) 3541-4618</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>559935414618</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:28</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:28</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q229" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R229" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>94AAE6F199BB109B6D60</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>MOTOPLENA</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>(99) 3541-3839</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>559935413839</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:29</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:29</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="O230" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q230" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R230" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>3EB0AC56DA05D8050FC113</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Soares Moto peças</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>(99) 98838-5327</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>5599988385327</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:31</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:31</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr"/>
+      <c r="N231" t="inlineStr"/>
+      <c r="O231" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q231" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R231" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T231" t="inlineStr">
+        <is>
+          <t>3EB0D0619D0AB3F34FD200</t>
+        </is>
+      </c>
+      <c r="U231" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>Gilberto Moto Peças</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>(99) 99641-6975</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>5599996416975</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:32</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:32</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr"/>
+      <c r="N232" t="inlineStr"/>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q232" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R232" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>3EB06668AFD0A4A5D547C6</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>Estilo Motos</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>(99) 98112-7701</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>5599981127701</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:34</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:34</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr"/>
+      <c r="N233" t="inlineStr"/>
+      <c r="O233" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q233" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>3EB031CBCA24BAF2FB5461</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>WT MOTO PEÇAS</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>(99) 99179-5139</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>5599991795139</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:35</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:35</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr"/>
+      <c r="N234" t="inlineStr"/>
+      <c r="O234" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q234" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R234" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>3EB0DF25015F1C757ED4F9</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>RS Moto peças</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>(99) 98404-6519</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>5599984046519</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:37</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:37</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr"/>
+      <c r="N235" t="inlineStr"/>
+      <c r="O235" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q235" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R235" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>3EB06458C1A9D64EE404DA</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>Ernestino Motos</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Loja</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>(99) 98197-7822</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>5599981977822</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:38</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:38</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr"/>
+      <c r="N236" t="inlineStr"/>
+      <c r="O236" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q236" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R236" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>3EB0B93D7C0C1CEF45C73C</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>Israel Motos</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Escritório da empresa</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>(99) 98453-2750</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>5599984532750</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:40</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:40</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr"/>
+      <c r="N237" t="inlineStr"/>
+      <c r="O237" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q237" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R237" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>3EB01FD81C2AE7E1890C4A</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>Prestige Motos</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>(99) 98852-8310</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>5599988528310</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>BALSAS</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:41</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:41</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr"/>
+      <c r="N238" t="inlineStr"/>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q238" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R238" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>3EB0BFC7081F56C0FB8743</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>TKL MOTOS</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>(99) 99197-5484</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>5599991975484</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:43</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:43</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr"/>
+      <c r="N239" t="inlineStr"/>
+      <c r="O239" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q239" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R239" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>3EB0739B0D96E1C5DCB98A</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Mega conserto de motos</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>(99) 98508-3121</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>5599985083121</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:44</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:44</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr"/>
+      <c r="N240" t="inlineStr"/>
+      <c r="O240" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q240" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R240" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>3EB04407777A56DAEADC5D</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PERFIL PEÇAS</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Loja de bicicleta</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>(99) 98180-5523</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>5599981805523</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:46</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:46</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+      <c r="N241" t="inlineStr"/>
+      <c r="O241" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q241" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R241" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>3EB0CB290609C6A6E9F506</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Nenem motos</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>(99) 99145-9244</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>5599991459244</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:47</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:47</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr"/>
+      <c r="N242" t="inlineStr"/>
+      <c r="O242" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q242" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R242" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>3EB03BB47BFD28111D3CBA</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Tontoy Motos - Moto Peças - Oficina Amazonas</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>(33) 99802-7296</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>5533998027296</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:49</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>19/05/2026 10:49</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr"/>
+      <c r="N243" t="inlineStr"/>
+      <c r="O243" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q243" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R243" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>E761CEB7F383F04DA888</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/data/disparo_atacado.xlsx
+++ b/templates/data/disparo_atacado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U243"/>
+  <dimension ref="A1:U258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20757,6 +20757,1371 @@
         </is>
       </c>
     </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>M.W.M Moto Peças</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>(99) 99151-1480</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>5599991511480</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:12</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:12</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr"/>
+      <c r="N244" t="inlineStr"/>
+      <c r="O244" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q244" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R244" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>3EB067B77CB41709424DEF</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>Mundial Motos</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>(99) 98257-4335</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>5599982574335</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:13</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:13</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr"/>
+      <c r="N245" t="inlineStr"/>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>3EB0219CC47599B8A4CB9D</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>A+Moto</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>(99) 98126-2557</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>5599981262557</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:15</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:15</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+      <c r="N246" t="inlineStr"/>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>1990BDC50CBA8D42F726</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Comercial Motos 3 Irmãos</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>(99) 98817-0045</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>5599988170045</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:16</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:16</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr"/>
+      <c r="N247" t="inlineStr"/>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>3EB08FBB091A58CAAB818C</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Rio motos</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>(99) 3526-3448</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>559935263448</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:18</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:18</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr"/>
+      <c r="N248" t="inlineStr"/>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>3EB03A7130902C7665D3E7</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>JL MOTOS</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Mecânico</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>(99) 99174-7318</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>5599991747318</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:19</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:19</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr"/>
+      <c r="N249" t="inlineStr"/>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>3EB0A72F547FEE8CC2BD0C</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Honda Motoca</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Concessionária Honda</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>(99) 2101-0500</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>559921010500</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:21</t>
+        </is>
+      </c>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:21</t>
+        </is>
+      </c>
+      <c r="M250" t="inlineStr"/>
+      <c r="N250" t="inlineStr"/>
+      <c r="O250" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q250" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R250" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S250" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>3EB0C4A798876519109302</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Chico Motopeças</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Loja de motocicletas</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>(99) 3524-7409</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>559935247409</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:22</t>
+        </is>
+      </c>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:22</t>
+        </is>
+      </c>
+      <c r="M251" t="inlineStr"/>
+      <c r="N251" t="inlineStr"/>
+      <c r="O251" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q251" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R251" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S251" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>3EB0064C549ABF574D4E9C</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Moto Peças Menezes</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>(99) 98120-5421</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>5599981205421</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:24</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:24</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+      <c r="N252" t="inlineStr"/>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R252" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S252" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>3EB09E298D1D50C5E808F8</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Casé Motos</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Loja</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>(63) 99259-6376</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>5563992596376</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:25</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:25</t>
+        </is>
+      </c>
+      <c r="M253" t="inlineStr"/>
+      <c r="N253" t="inlineStr"/>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R253" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S253" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>3EB0B28310E5FB7A2CCA32</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Outfit Motos</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>(99) 99219-2337</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>5599992192337</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:27</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:27</t>
+        </is>
+      </c>
+      <c r="M254" t="inlineStr"/>
+      <c r="N254" t="inlineStr"/>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R254" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S254" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>3EB049D86B18680C2A94BE</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Rossi Motors</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>(99) 98526-3909</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>5599985263909</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:28</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:28</t>
+        </is>
+      </c>
+      <c r="M255" t="inlineStr"/>
+      <c r="N255" t="inlineStr"/>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R255" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S255" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>3EB0A67B6430BC596709A0</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Auto Peças Imperatriz</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Loja de autopeças</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>(99) 98257-0154</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>5599982570154</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:30</t>
+        </is>
+      </c>
+      <c r="M256" t="inlineStr"/>
+      <c r="N256" t="inlineStr"/>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R256" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S256" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>3EB0D3451EB79FA0B4ED35</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Mottu Imperatriz</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Agência de aluguel de motocicletas</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>(11) 3181-8188</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>551131818188</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:31</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:31</t>
+        </is>
+      </c>
+      <c r="M257" t="inlineStr"/>
+      <c r="N257" t="inlineStr"/>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R257" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S257" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>3EB06739715861CAB0447F</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Gr Motos</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>(99) 99179-1295</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>5599991791295</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>IMPERATRIZ</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:33</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>20/05/2026 08:33</t>
+        </is>
+      </c>
+      <c r="M258" t="inlineStr"/>
+      <c r="N258" t="inlineStr"/>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S258" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>3EB07ECFF03F927674B6C3</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/templates/data/disparo_atacado.xlsx
+++ b/templates/data/disparo_atacado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U258"/>
+  <dimension ref="A1:U281"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22122,6 +22122,2063 @@
         </is>
       </c>
     </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>AF MOTOS RACING</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>(94) 98427-7568</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>5594984277568</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:49</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:49</t>
+        </is>
+      </c>
+      <c r="M259" t="inlineStr"/>
+      <c r="N259" t="inlineStr"/>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R259" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S259" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>F6BBA5D945D7E04B7601</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>André Motos Filial Cidade Nova</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>(94) 99126-5229</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>5594991265229</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:51</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr"/>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:51</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr"/>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R260" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>3EB064B4D772509B370546</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Phoenix Motocenter</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>(94) 99290-6517</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>5594992906517</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>MARABA</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:52</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr"/>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:52</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr"/>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R261" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>3EB08B9943845BE12F8B8E</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Luan Motos Peças e Acessórios</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Loja de autopeças</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>(94) 99285-9640</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>5594992859640</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:54</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr"/>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:54</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr"/>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>3EB0DFD66FC55E2C80B75E</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>JJ Moto Peças Parauapebas - Rio Verde</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>(94) 99285-6543</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>5594992856543</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:55</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr"/>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:55</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr"/>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>3EB050388C7F4BBF6D7735</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Rede ANCORA Moral Autopeças PA</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Loja de autopeças</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>(94) 99175-9554</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>5594991759554</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:57</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr"/>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:57</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr"/>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>3EB0E3F8BD8801846490EA</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>KM MOTO PARTS</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>(94) 99199-3111</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>5594991993111</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:58</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr"/>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>20/05/2026 13:58</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr"/>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>3EB06043448DF701666D92</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Fashion Motos Peças e Serviços</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>(94) 99173-6423</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>5594991736423</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:00</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr"/>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:00</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr"/>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>3EB0E0C409515E204244F4</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Atacado Delivery Moto Pecas</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Atacadista</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>(94) 99297-6481</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>5594992976481</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:01</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr"/>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:01</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr"/>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>3EB048D08AC87CB852C0BD</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>CM Ciclo Motos – Peças e Acessórios para Motos</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>(94) 99105-2369</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>5594991052369</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr"/>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:03</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr"/>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>3EB06A828E3DE6DE94F95A</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Atacadão Moto Peças</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>(94) 99106-4704</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>5594991064704</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:04</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr"/>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:04</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr"/>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>3EB070F47BF616FD67B217</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Magnos Moto peças</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>(94) 99249-5478</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>5594992495478</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:06</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr"/>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:06</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr"/>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>3EB0C2EA891B2FCDBB9BE1</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Central Moto Peças</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>(94) 99250-5571</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>5594992505571</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:07</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr"/>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:07</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr"/>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>3EB039E9F48BB0EB09987D</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>André Motos Canaã dos Carajás</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>(94) 98414-2545</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>5594984142545</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:09</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr"/>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:09</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr"/>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>3EB065665AD5FB5EB60F1A</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Moto Peças Cacique</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>(94) 99227-1045</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>5594992271045</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:10</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr"/>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:10</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr"/>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>2928AE82B7CCEF519D0F</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Variedade Moto Peças</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>(94) 99161-3489</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>5594991613489</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:12</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr"/>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:12</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr"/>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>3EB0523D4D26353D88ECDA</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Lary Motos</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>(94) 99240-3117</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>5594992403117</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr"/>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:13</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr"/>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>3EB05F250D55F3B20CF43C</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>AD Motos</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Loja de peças para motocicletas</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>(94) 99159-4384</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>5594991594384</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:15</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr"/>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:15</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr"/>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>3EB05362DB76F7B0840710</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>dinamity moto peças</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>(94) 99268-4691</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>5594992684691</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:16</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr"/>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:16</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr"/>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>3EB09FD5EADB7562A2683B</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Tocantins Moto</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Oficina mecânica</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>(94) 99168-1916</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>5594991681916</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:18</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr"/>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:18</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr"/>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>3EB06838384DC177FBB90E</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Alto Giro Moto Peças</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>(94) 98416-3642</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>5594984163642</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:19</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr"/>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:19</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr"/>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>3EB04CF06DF8CEF01BFADE</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Alto Giro Moto-Peças</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Oficina mecânica de motos</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>(94) 98416-3642</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>5594984163642</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>DUPLICADO</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr"/>
+      <c r="K280" t="inlineStr"/>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr"/>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Telefone duplicado na planilha ou execução</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr"/>
+      <c r="Q280" t="inlineStr"/>
+      <c r="R280" t="inlineStr"/>
+      <c r="S280" t="inlineStr"/>
+      <c r="T280" t="inlineStr"/>
+      <c r="U280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Vitória Moto Peças</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Loja</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>(94) 99120-9676</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>5594991209676</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>CANAA</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>ENVIADO</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:21</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>AGUARDANDO</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr"/>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>20/05/2026 14:21</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr"/>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>Disparo atacado enviado com sucesso via botões Z-API</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>CAMPANHA_ATACADO_BOTOES</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>atacado</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>AGUARDAR_RETORNO</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>MORNO</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>3EB0A7DF38EEEF2910F138</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>BOTOES</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
